--- a/docs/testing/StageArt_WebBeta_TestCases.xlsx
+++ b/docs/testing/StageArt_WebBeta_TestCases.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G80"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1193,252 +1193,252 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SEARCH-01</v>
+        <v>PUBLIC-URL-001</v>
       </c>
       <c r="B35" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C35" t="str">
-        <v>Organization search, unauthenticated</v>
+        <v>Organization official URL</v>
       </c>
       <c r="D35" t="str">
-        <v>Published demo org exists</v>
+        <v>Published Organization with slug `sample-theatre-company`</v>
       </c>
       <c r="E35" t="str">
-        <v>`GET /organizations/search?q=...`</v>
+        <v>Browser: `/sample-theatre-company` (or `stageart.top/sample-theatre-company` once deployed there)</v>
       </c>
       <c r="F35" t="str">
-        <v>Matching published org(s) returned; unpublished never appear</v>
+        <v>Organization Public Page renders (name, description, production lists)</v>
       </c>
       <c r="G35" t="str">
-        <v>Live curl this session</v>
+        <v>Manual browser check required; route existence confirmed via `expo export` (36 static routes incl. `/[organizationSlug]`)</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SEARCH-02</v>
+        <v>PUBLIC-URL-002</v>
       </c>
       <c r="B36" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C36" t="str">
-        <v>Production search, unauthenticated</v>
+        <v>Production official URL</v>
       </c>
       <c r="D36" t="str">
-        <v>Published demo production exists</v>
+        <v>Published Production with slug `sample-summer-show` under `sample-theatre-company`</v>
       </c>
       <c r="E36" t="str">
-        <v>`GET /productions/search?q=...`</v>
+        <v>Browser: `/sample-theatre-company/sample-summer-show`</v>
       </c>
       <c r="F36" t="str">
-        <v>Matching published production(s) returned; unpublished never appear</v>
+        <v>Production Public Page renders (name, title heading, parent Organization link)</v>
       </c>
       <c r="G36" t="str">
-        <v>Live curl this session</v>
+        <v>Manual browser check required; route existence confirmed via `expo export` (`/[organizationSlug]/[productionSlug]`)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SEARCH-03</v>
+        <v>PUBLIC-URL-003</v>
       </c>
       <c r="B37" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C37" t="str">
-        <v>Empty/whitespace query</v>
+        <v>Unauthenticated viewing</v>
       </c>
       <c r="D37" t="str">
-        <v>Any</v>
+        <v>Not logged in</v>
       </c>
       <c r="E37" t="str">
-        <v>Submit search with no text</v>
+        <v>Visit PUBLIC-URL-001/002's URLs with no session</v>
       </c>
       <c r="F37" t="str">
-        <v>Empty result, no error</v>
+        <v>Pages render fully; Follow/Favorite/Membership-request controls show a "ログインして..." prompt instead of being hidden entirely</v>
       </c>
       <c r="G37" t="str">
-        <v>`SearchOrganizationsUseCaseTest` / `SearchProductionsUseCaseTest`</v>
+        <v>Live curl this session (unauthenticated GET succeeds); `public-organization-login-to-follow` testID exists in code</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MEM-01</v>
+        <v>PUBLIC-URL-004</v>
       </c>
       <c r="B38" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C38" t="str">
-        <v>Request Organization membership via search</v>
+        <v>PUBLISHED is viewable</v>
       </c>
       <c r="D38" t="str">
-        <v>Logged in, published Org found via search</v>
+        <v>Organization/Production with `published_at` in the past</v>
       </c>
       <c r="E38" t="str">
-        <v>View org public page → request membership</v>
+        <v>`GET /organizations/by-slug/{slug}` / `/productions/by-slug/{slug}`</v>
       </c>
       <c r="F38" t="str">
-        <v>Membership row created, status REQUESTED</v>
+        <v>200</v>
       </c>
       <c r="G38" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MEM-02</v>
+        <v>PUBLIC-URL-005</v>
       </c>
       <c r="B39" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C39" t="str">
-        <v>Admin approves pending request</v>
+        <v>DRAFT is not viewable</v>
       </c>
       <c r="D39" t="str">
-        <v>Owner, REQUESTED Membership exists</v>
+        <v>Organization/Production with `published_at = null`</v>
       </c>
       <c r="E39" t="str">
-        <v>Approve from pending-requests list</v>
+        <v>Same requests</v>
       </c>
       <c r="F39" t="str">
-        <v>Status → ACTIVE, `joined_at` set</v>
+        <v>404, identical to a nonexistent slug</v>
       </c>
       <c r="G39" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>`GetPublicOrganizationBySlugUseCaseTest` / `GetPublicProductionBySlugUseCaseTest`</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MEM-03</v>
+        <v>PUBLIC-URL-006</v>
       </c>
       <c r="B40" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C40" t="str">
-        <v>Admin rejects pending request</v>
+        <v>SCHEDULED before its publish date</v>
       </c>
       <c r="D40" t="str">
-        <v>Owner, REQUESTED Membership exists</v>
+        <v>`published_at` set to a future datetime</v>
       </c>
       <c r="E40" t="str">
-        <v>Reject from pending-requests list</v>
+        <v>Same requests</v>
       </c>
       <c r="F40" t="str">
-        <v>Status → REJECTED</v>
+        <v>404 - not yet visible, same as DRAFT</v>
       </c>
       <c r="G40" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>Live curl this session (PUT with future `published_at` → GET by-slug → 404); `test_scheduled_organization_before_its_publish_date_is_not_found` / `test_scheduled_production_before_its_publish_date_is_not_found`</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MEM-04</v>
+        <v>PUBLIC-URL-007</v>
       </c>
       <c r="B41" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C41" t="str">
-        <v>Re-request after rejection</v>
+        <v>SCHEDULED after its publish date</v>
       </c>
       <c r="D41" t="str">
-        <v>Previously REJECTED Membership</v>
+        <v>`published_at` set to a past/now datetime (previously future, time has passed)</v>
       </c>
       <c r="E41" t="str">
-        <v>Request again</v>
+        <v>Same requests</v>
       </c>
       <c r="F41" t="str">
-        <v>New Membership row created (REQUESTED); old REJECTED row kept as history, no unique-constraint conflict</v>
+        <v>200 - now visible, same as an immediately-published item</v>
       </c>
       <c r="G41" t="str">
-        <v>`MembershipTest.php` (Domain), confirms `requestMembership()`/`approve()`/`reject()` state guards</v>
+        <v>Live curl this session (PUT with past `published_at` → GET by-slug → 200); `test_scheduled_organization_after_its_publish_date_is_visible` / `test_scheduled_production_after_its_publish_date_is_visible`</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MEM-05</v>
+        <v>PUBLIC-URL-008</v>
       </c>
       <c r="B42" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C42" t="str">
-        <v>List my memberships (real HTTP)</v>
+        <v>ARCHIVED Production handling</v>
       </c>
       <c r="D42" t="str">
-        <v>Logged in</v>
+        <v>Production Lifecycle status ARCHIVED, still published</v>
       </c>
       <c r="E42" t="str">
-        <v>`GET /me/memberships` with real Bearer token</v>
+        <v>`GET /productions/by-slug/{slug}`</v>
       </c>
       <c r="F42" t="str">
-        <v>Returns this Person's Membership rows with correct statuses</v>
+        <v>200 - publication state (`published_at`) is independent of Lifecycle `status`; an ARCHIVED Production's public page keeps showing as a record, per `PublicSiteLifecycle.md`'s "公演終了後もProduction Public Siteは削除せず"</v>
       </c>
       <c r="G42" t="str">
-        <v>Live curl this session</v>
+        <v>Live curl this session (seed's `sample-last-years-show`, status ARCHIVED, published, resolves 200); appears in its Organization's "過去の公演" list (`status` proxy, see `PublicOrganizationProductionSummary`)</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MEM-06</v>
+        <v>PUBLIC-URL-009</v>
       </c>
       <c r="B43" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C43" t="str">
-        <v>List pending requests (real HTTP)</v>
+        <v>Search result → Public Page navigation</v>
       </c>
       <c r="D43" t="str">
-        <v>Owner, at least one REQUESTED Membership</v>
+        <v>Search returns a published Organization/Production</v>
       </c>
       <c r="E43" t="str">
-        <v>`GET /organizations/{id}/membership-requests` with real Bearer token</v>
+        <v>Tap a search result on `/discover-organizations` or `/discover-productions`</v>
       </c>
       <c r="F43" t="str">
-        <v>Returns the REQUESTED row</v>
+        <v>Navigates to `/{organization-slug}` or `/{organization-slug}/{production-slug}` (root-level URL, not the old `/o/{slug}` prefix)</v>
       </c>
       <c r="G43" t="str">
-        <v>Live curl this session</v>
+        <v>tsc/lint clean on the updated `router.push()` call sites; manual browser click-through still required</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>JOIN-01</v>
+        <v>PUBLIC-URL-010</v>
       </c>
       <c r="B44" t="str">
-        <v>JOIN KEY</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C44" t="str">
-        <v>Issue Organization Join Key</v>
+        <v>Favorite from the Public Page</v>
       </c>
       <c r="D44" t="str">
-        <v>Owner</v>
+        <v>Logged in, viewing a published Organization/Production page</v>
       </c>
       <c r="E44" t="str">
-        <v>Issue a Join Key</v>
+        <v>Tap お気に入りに追加/解除</v>
       </c>
       <c r="F44" t="str">
-        <v>8-character code returned, status ACTIVE</v>
+        <v>Favorite toggles; reflected in `/favorites`, whose own links now also point to the root-level URL</v>
       </c>
       <c r="G44" t="str">
-        <v>Live curl this session</v>
+        <v>Live curl this session (POST/DELETE /favorites); `favorites.tsx`'s `targetHref()` updated to root-level paths</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>JOIN-02</v>
+        <v>SEARCH-01</v>
       </c>
       <c r="B45" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C45" t="str">
-        <v>Issue Production Join Key</v>
+        <v>Organization search, unauthenticated</v>
       </c>
       <c r="D45" t="str">
-        <v>PrimaryManager</v>
+        <v>Published demo org exists</v>
       </c>
       <c r="E45" t="str">
-        <v>Issue a Join Key</v>
+        <v>`GET /organizations/search?q=...`</v>
       </c>
       <c r="F45" t="str">
-        <v>8-character code returned</v>
+        <v>Matching published org(s) returned; unpublished never appear</v>
       </c>
       <c r="G45" t="str">
         <v>Live curl this session</v>
@@ -1446,160 +1446,160 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>JOIN-03</v>
+        <v>SEARCH-02</v>
       </c>
       <c r="B46" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C46" t="str">
-        <v>Resolve a Join Key</v>
+        <v>Production search, unauthenticated</v>
       </c>
       <c r="D46" t="str">
-        <v>Valid code</v>
+        <v>Published demo production exists</v>
       </c>
       <c r="E46" t="str">
-        <v>`POST /join-keys/resolve`</v>
+        <v>`GET /productions/search?q=...`</v>
       </c>
       <c r="F46" t="str">
-        <v>Returns target type (ORGANIZATION/PRODUCTION) + target identity, does not create a Membership/Participant yet</v>
+        <v>Matching published production(s) returned; unpublished never appear</v>
       </c>
       <c r="G46" t="str">
-        <v>`ResolveJoinKeyUseCase` Application test</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>JOIN-04</v>
+        <v>SEARCH-03</v>
       </c>
       <c r="B47" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C47" t="str">
-        <v>Join via code → request created</v>
+        <v>Empty/whitespace query</v>
       </c>
       <c r="D47" t="str">
-        <v>Valid, usable code</v>
+        <v>Any</v>
       </c>
       <c r="E47" t="str">
-        <v>Enter code on `/join`, confirm</v>
+        <v>Submit search with no text</v>
       </c>
       <c r="F47" t="str">
-        <v>Membership or Participant request created in the correct pending state</v>
+        <v>Empty result, no error</v>
       </c>
       <c r="G47" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>`SearchOrganizationsUseCaseTest` / `SearchProductionsUseCaseTest`</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JOIN-05</v>
+        <v>MEM-01</v>
       </c>
       <c r="B48" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C48" t="str">
-        <v>Disable a Join Key</v>
+        <v>Request Organization membership via search</v>
       </c>
       <c r="D48" t="str">
-        <v>ACTIVE key exists</v>
+        <v>Logged in, published Org found via search</v>
       </c>
       <c r="E48" t="str">
-        <v>Disable it</v>
+        <v>View org public page → request membership</v>
       </c>
       <c r="F48" t="str">
-        <v>Status → DISABLED; further resolve/use attempts fail; past Memberships/Participants from it are not retroactively removed</v>
+        <v>Membership row created, status REQUESTED</v>
       </c>
       <c r="G48" t="str">
-        <v>`JoinKeyTest.php` (Domain)</v>
+        <v>`rest_do_request` in-process E2E</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>JOIN-06</v>
+        <v>MEM-02</v>
       </c>
       <c r="B49" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C49" t="str">
-        <v>Expired/exhausted key rejected</v>
+        <v>Admin approves pending request</v>
       </c>
       <c r="D49" t="str">
-        <v>Key past `expires_at` or at `max_uses`</v>
+        <v>Owner, REQUESTED Membership exists</v>
       </c>
       <c r="E49" t="str">
-        <v>Attempt to use</v>
+        <v>Approve from pending-requests list</v>
       </c>
       <c r="F49" t="str">
-        <v>Rejected, `isUsable()` false</v>
+        <v>Status → ACTIVE, `joined_at` set</v>
       </c>
       <c r="G49" t="str">
-        <v>`JoinKeyTest.php` (Domain)</v>
+        <v>`rest_do_request` in-process E2E</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>JOIN-07</v>
+        <v>MEM-03</v>
       </c>
       <c r="B50" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C50" t="str">
-        <v>QR is a representation of Join Key, not a separate identity</v>
+        <v>Admin rejects pending request</v>
       </c>
       <c r="D50" t="str">
-        <v>N/A</v>
+        <v>Owner, REQUESTED Membership exists</v>
       </c>
       <c r="E50" t="str">
-        <v>(Design confirmation, not a runtime test)</v>
+        <v>Reject from pending-requests list</v>
       </c>
       <c r="F50" t="str">
-        <v>QR encodes the Join Key/URL only; scanning still routes through the same resolve→confirm→request flow</v>
+        <v>Status → REJECTED</v>
       </c>
       <c r="G50" t="str">
-        <v>`docs/04-DomainModel/JoinKey.md` §"QR Code" (Blueprint, unimplemented UI - camera/QR decode not built)</v>
+        <v>`rest_do_request` in-process E2E</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>FAV-01</v>
+        <v>MEM-04</v>
       </c>
       <c r="B51" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C51" t="str">
-        <v>Favorite an Organization</v>
+        <v>Re-request after rejection</v>
       </c>
       <c r="D51" t="str">
-        <v>Logged in, published org</v>
+        <v>Previously REJECTED Membership</v>
       </c>
       <c r="E51" t="str">
-        <v>POST /favorites (ORGANIZATION)</v>
+        <v>Request again</v>
       </c>
       <c r="F51" t="str">
-        <v>Row created; appears in `/me/favorites`</v>
+        <v>New Membership row created (REQUESTED); old REJECTED row kept as history, no unique-constraint conflict</v>
       </c>
       <c r="G51" t="str">
-        <v>Live curl this session</v>
+        <v>`MembershipTest.php` (Domain), confirms `requestMembership()`/`approve()`/`reject()` state guards</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>FAV-02</v>
+        <v>MEM-05</v>
       </c>
       <c r="B52" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C52" t="str">
-        <v>Favorite a Production</v>
+        <v>List my memberships (real HTTP)</v>
       </c>
       <c r="D52" t="str">
-        <v>Logged in, published production</v>
+        <v>Logged in</v>
       </c>
       <c r="E52" t="str">
-        <v>POST /favorites (PRODUCTION)</v>
+        <v>`GET /me/memberships` with real Bearer token</v>
       </c>
       <c r="F52" t="str">
-        <v>Row created, resolves parent org slug</v>
+        <v>Returns this Person's Membership rows with correct statuses</v>
       </c>
       <c r="G52" t="str">
         <v>Live curl this session</v>
@@ -1607,22 +1607,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FAV-03</v>
+        <v>MEM-06</v>
       </c>
       <c r="B53" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C53" t="str">
-        <v>Remove a Favorite</v>
+        <v>List pending requests (real HTTP)</v>
       </c>
       <c r="D53" t="str">
-        <v>Favorite exists</v>
+        <v>Owner, at least one REQUESTED Membership</v>
       </c>
       <c r="E53" t="str">
-        <v>DELETE /favorites?target_type=...&amp;target_id=...</v>
+        <v>`GET /organizations/{id}/membership-requests` with real Bearer token</v>
       </c>
       <c r="F53" t="str">
-        <v>Row removed; repeat call is a harmless no-op</v>
+        <v>Returns the REQUESTED row</v>
       </c>
       <c r="G53" t="str">
         <v>Live curl this session</v>
@@ -1630,405 +1630,635 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>FAV-04</v>
+        <v>JOIN-01</v>
       </c>
       <c r="B54" t="str">
-        <v>FAVORITE</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C54" t="str">
-        <v>Cannot favorite an unpublished target</v>
+        <v>Issue Organization Join Key</v>
       </c>
       <c r="D54" t="str">
-        <v>Draft Production</v>
+        <v>Owner</v>
       </c>
       <c r="E54" t="str">
-        <v>POST /favorites against it</v>
+        <v>Issue a Join Key</v>
       </c>
       <c r="F54" t="str">
-        <v>Rejected (not found/not public)</v>
+        <v>8-character code returned, status ACTIVE</v>
       </c>
       <c r="G54" t="str">
-        <v>`AddFavoriteUseCase` Application test</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>REH-01</v>
+        <v>JOIN-02</v>
       </c>
       <c r="B55" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C55" t="str">
-        <v>Create a Rehearsal</v>
+        <v>Issue Production Join Key</v>
       </c>
       <c r="D55" t="str">
-        <v>PrimaryManager, published Production</v>
+        <v>PrimaryManager</v>
       </c>
       <c r="E55" t="str">
-        <v>Fill title/date/place → save</v>
+        <v>Issue a Join Key</v>
       </c>
       <c r="F55" t="str">
-        <v>Rehearsal created, SCHEDULED</v>
+        <v>8-character code returned</v>
       </c>
       <c r="G55" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>REH-02</v>
+        <v>JOIN-03</v>
       </c>
       <c r="B56" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C56" t="str">
-        <v>Confirm a Rehearsal</v>
+        <v>Resolve a Join Key</v>
       </c>
       <c r="D56" t="str">
-        <v>SCHEDULED Rehearsal</v>
+        <v>Valid code</v>
       </c>
       <c r="E56" t="str">
-        <v>Confirm</v>
+        <v>`POST /join-keys/resolve`</v>
       </c>
       <c r="F56" t="str">
-        <v>Status → CONFIRMED; Phase 2 Attendance records generated for active members</v>
+        <v>Returns target type (ORGANIZATION/PRODUCTION) + target identity, does not create a Membership/Participant yet</v>
       </c>
       <c r="G56" t="str">
-        <v>`rest_do_request` in-process E2E, `Rehearsal.php` Domain guard (only SCHEDULED can confirm)</v>
+        <v>`ResolveJoinKeyUseCase` Application test</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>REH-03</v>
+        <v>JOIN-04</v>
       </c>
       <c r="B57" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C57" t="str">
-        <v>Full lifecycle: confirm → activate → complete</v>
+        <v>Join via code → request created</v>
       </c>
       <c r="D57" t="str">
-        <v>SCHEDULED Rehearsal</v>
+        <v>Valid, usable code</v>
       </c>
       <c r="E57" t="str">
-        <v>Run all 3 transitions</v>
+        <v>Enter code on `/join`, confirm</v>
       </c>
       <c r="F57" t="str">
-        <v>Status advances correctly, rejects out-of-order calls</v>
+        <v>Membership or Participant request created in the correct pending state</v>
       </c>
       <c r="G57" t="str">
-        <v>Domain-level status-guard unit tests</v>
+        <v>`rest_do_request` in-process E2E</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>REH-04</v>
+        <v>JOIN-05</v>
       </c>
       <c r="B58" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C58" t="str">
-        <v>Edit basic info on a non-terminal Rehearsal</v>
+        <v>Disable a Join Key</v>
       </c>
       <c r="D58" t="str">
-        <v>SCHEDULED/CONFIRMED/ACTIVE Rehearsal</v>
+        <v>ACTIVE key exists</v>
       </c>
       <c r="E58" t="str">
-        <v>Edit title/date/location</v>
+        <v>Disable it</v>
       </c>
       <c r="F58" t="str">
-        <v>Updated</v>
+        <v>Status → DISABLED; further resolve/use attempts fail; past Memberships/Participants from it are not retroactively removed</v>
       </c>
       <c r="G58" t="str">
-        <v>`Rehearsal.php` Domain test</v>
+        <v>`JoinKeyTest.php` (Domain)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>REH-05</v>
+        <v>JOIN-06</v>
       </c>
       <c r="B59" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C59" t="str">
-        <v>Cannot edit a COMPLETED/CANCELLED Rehearsal</v>
+        <v>Expired/exhausted key rejected</v>
       </c>
       <c r="D59" t="str">
-        <v>Terminal-state Rehearsal</v>
+        <v>Key past `expires_at` or at `max_uses`</v>
       </c>
       <c r="E59" t="str">
-        <v>Attempt edit</v>
+        <v>Attempt to use</v>
       </c>
       <c r="F59" t="str">
-        <v>Rejected</v>
+        <v>Rejected, `isUsable()` false</v>
       </c>
       <c r="G59" t="str">
-        <v>`Rehearsal.php` Domain test</v>
+        <v>`JoinKeyTest.php` (Domain)</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ATT-01</v>
+        <v>JOIN-07</v>
       </c>
       <c r="B60" t="str">
-        <v>ATTENDANCE</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C60" t="str">
-        <v>Unconfirmed Rehearsal shows no response control</v>
+        <v>QR is a representation of Join Key, not a separate identity</v>
       </c>
       <c r="D60" t="str">
-        <v>Participant, unconfirmed Rehearsal</v>
+        <v>N/A</v>
       </c>
       <c r="E60" t="str">
-        <v>View it</v>
+        <v>(Design confirmation, not a runtime test)</v>
       </c>
       <c r="F60" t="str">
-        <v>No attendance-response entry point shown</v>
+        <v>QR encodes the Join Key/URL only; scanning still routes through the same resolve→confirm→request flow</v>
       </c>
       <c r="G60" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>`docs/04-DomainModel/JoinKey.md` §"QR Code" (Blueprint, unimplemented UI - camera/QR decode not built)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ATT-02</v>
+        <v>FAV-01</v>
       </c>
       <c r="B61" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C61" t="str">
-        <v>Confirmed Rehearsal shows response control</v>
+        <v>Favorite an Organization</v>
       </c>
       <c r="D61" t="str">
-        <v>Participant, confirmed Rehearsal</v>
+        <v>Logged in, published org</v>
       </c>
       <c r="E61" t="str">
-        <v>View it</v>
+        <v>POST /favorites (ORGANIZATION)</v>
       </c>
       <c r="F61" t="str">
-        <v>Attendance-response entry point appears</v>
+        <v>Row created; appears in `/me/favorites`</v>
       </c>
       <c r="G61" t="str">
-        <v>`rest_do_request` in-process E2E</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ATT-03</v>
+        <v>FAV-02</v>
       </c>
       <c r="B62" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C62" t="str">
-        <v>Manager views per-member attendance status</v>
+        <v>Favorite a Production</v>
       </c>
       <c r="D62" t="str">
-        <v>PrimaryManager, confirmed Rehearsal with responses</v>
+        <v>Logged in, published production</v>
       </c>
       <c r="E62" t="str">
-        <v>Open attendance summary</v>
+        <v>POST /favorites (PRODUCTION)</v>
       </c>
       <c r="F62" t="str">
-        <v>Correct per-member status list</v>
+        <v>Row created, resolves parent org slug</v>
       </c>
       <c r="G62" t="str">
-        <v>`ListRehearsalAttendancesUseCase` Application test</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ATT-04</v>
+        <v>FAV-03</v>
       </c>
       <c r="B63" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C63" t="str">
-        <v>Respond to attendance</v>
+        <v>Remove a Favorite</v>
       </c>
       <c r="D63" t="str">
-        <v>Participant, confirmed Rehearsal</v>
+        <v>Favorite exists</v>
       </c>
       <c r="E63" t="str">
-        <v>Submit a response</v>
+        <v>DELETE /favorites?target_type=...&amp;target_id=...</v>
       </c>
       <c r="F63" t="str">
-        <v>`RehearsalAttendance` status updated</v>
+        <v>Row removed; repeat call is a harmless no-op</v>
       </c>
       <c r="G63" t="str">
-        <v>`RespondRehearsalAttendanceUseCase` Application test</v>
+        <v>Live curl this session</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ROLE-01</v>
+        <v>FAV-04</v>
       </c>
       <c r="B64" t="str">
-        <v>ROLE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C64" t="str">
-        <v>One Person holds multiple simultaneous roles</v>
+        <v>Cannot favorite an unpublished target</v>
       </c>
       <c r="D64" t="str">
-        <v>Seed data: `stageart_demo_production_manager` is both an Org A Member and the PrimaryManager of all 3 demo Productions</v>
+        <v>Draft Production</v>
       </c>
       <c r="E64" t="str">
-        <v>Inspect Memberships/Participants for that Person</v>
+        <v>POST /favorites against it</v>
       </c>
       <c r="F64" t="str">
-        <v>Multiple active role rows across different scopes coexist correctly</v>
+        <v>Rejected (not found/not public)</v>
       </c>
       <c r="G64" t="str">
-        <v>Direct DB read of seed data (this session)</v>
+        <v>`AddFavoriteUseCase` Application test</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ROLE-02</v>
+        <v>REH-01</v>
       </c>
       <c r="B65" t="str">
-        <v>ROLE</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C65" t="str">
-        <v>Organization ownership does not imply Production management</v>
+        <v>Create a Rehearsal</v>
       </c>
       <c r="D65" t="str">
-        <v>Org Owner not PrimaryManager of a given Production</v>
+        <v>PrimaryManager, published Production</v>
       </c>
       <c r="E65" t="str">
-        <v>Attempt a Production-management action as the Owner</v>
+        <v>Fill title/date/place → save</v>
       </c>
       <c r="F65" t="str">
-        <v>Denied</v>
+        <v>Rehearsal created, SCHEDULED</v>
       </c>
       <c r="G65" t="str">
-        <v>Live curl this session (see ORG-03)</v>
+        <v>`rest_do_request` in-process E2E</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ROLE-03</v>
+        <v>REH-02</v>
       </c>
       <c r="B66" t="str">
-        <v>ROLE</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C66" t="str">
-        <v>PrimaryManager-exclusive gate has no Organization-fallback path</v>
+        <v>Confirm a Rehearsal</v>
       </c>
       <c r="D66" t="str">
-        <v>`ProductionAuthorizationService::canManageProduction()`</v>
+        <v>SCHEDULED Rehearsal</v>
       </c>
       <c r="E66" t="str">
-        <v>Code review</v>
+        <v>Confirm</v>
       </c>
       <c r="F66" t="str">
-        <v>Exactly two paths: PrimaryManager, then ProductionDelegate - no third branch to Organization Membership</v>
+        <v>Status → CONFIRMED; Phase 2 Attendance records generated for active members</v>
       </c>
       <c r="G66" t="str">
-        <v>Source review, `docs/09-Authorization/Authorization.md`</v>
+        <v>`rest_do_request` in-process E2E, `Rehearsal.php` Domain guard (only SCHEDULED can confirm)</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SEED-01</v>
+        <v>REH-03</v>
       </c>
       <c r="B67" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C67" t="str">
-        <v>Seed script creates all 5 roles + edge states</v>
+        <v>Full lifecycle: confirm → activate → complete</v>
       </c>
       <c r="D67" t="str">
-        <v>Clean or previously-cleaned dev DB</v>
+        <v>SCHEDULED Rehearsal</v>
       </c>
       <c r="E67" t="str">
-        <v>Run `plugin/scripts/seed_web_beta.php`</v>
+        <v>Run all 3 transitions</v>
       </c>
       <c r="F67" t="str">
-        <v>7 demo users, 2 Orgs, 3 Productions (published/draft/archived), Memberships in ACTIVE/REQUESTED/REJECTED, Rehearsals with/without confirmation, 1 past-completed</v>
+        <v>Status advances correctly, rejects out-of-order calls</v>
       </c>
       <c r="G67" t="str">
-        <v>Ran this session, verified via direct DB reads - see `docs/testing/SeedData.md`</v>
+        <v>Domain-level status-guard unit tests</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SEED-02</v>
+        <v>REH-04</v>
       </c>
       <c r="B68" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C68" t="str">
-        <v>Cleanup removes only demo data</v>
+        <v>Edit basic info on a non-terminal Rehearsal</v>
       </c>
       <c r="D68" t="str">
-        <v>Seed data present, plus unrelated real data</v>
+        <v>SCHEDULED/CONFIRMED/ACTIVE Rehearsal</v>
       </c>
       <c r="E68" t="str">
-        <v>Run `seed_web_beta_cleanup.php`</v>
+        <v>Edit title/date/location</v>
       </c>
       <c r="F68" t="str">
-        <v>Only `stageart_demo_*` users and `[Sample]`-prefixed Orgs/Productions (and their dependents) removed; other data untouched</v>
+        <v>Updated</v>
       </c>
       <c r="G68" t="str">
-        <v>Ran this session - confirmed a real, non-demo Membership row survived cleanup untouched</v>
+        <v>`Rehearsal.php` Domain test</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SEED-03</v>
+        <v>REH-05</v>
       </c>
       <c r="B69" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C69" t="str">
-        <v>Cleanup is a no-op on a clean DB</v>
+        <v>Cannot edit a COMPLETED/CANCELLED Rehearsal</v>
       </c>
       <c r="D69" t="str">
-        <v>No demo data present</v>
+        <v>Terminal-state Rehearsal</v>
       </c>
       <c r="E69" t="str">
-        <v>Run cleanup</v>
+        <v>Attempt edit</v>
       </c>
       <c r="F69" t="str">
-        <v>Zero rows affected, no errors</v>
+        <v>Rejected</v>
       </c>
       <c r="G69" t="str">
-        <v>Ran this session</v>
+        <v>`Rehearsal.php` Domain test</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>ATT-01</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Unconfirmed Rehearsal shows no response control</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Participant, unconfirmed Rehearsal</v>
+      </c>
+      <c r="E70" t="str">
+        <v>View it</v>
+      </c>
+      <c r="F70" t="str">
+        <v>No attendance-response entry point shown</v>
+      </c>
+      <c r="G70" t="str">
+        <v>`rest_do_request` in-process E2E</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>ATT-02</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Confirmed Rehearsal shows response control</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Participant, confirmed Rehearsal</v>
+      </c>
+      <c r="E71" t="str">
+        <v>View it</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Attendance-response entry point appears</v>
+      </c>
+      <c r="G71" t="str">
+        <v>`rest_do_request` in-process E2E</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>ATT-03</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Manager views per-member attendance status</v>
+      </c>
+      <c r="D72" t="str">
+        <v>PrimaryManager, confirmed Rehearsal with responses</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Open attendance summary</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Correct per-member status list</v>
+      </c>
+      <c r="G72" t="str">
+        <v>`ListRehearsalAttendancesUseCase` Application test</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>ATT-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Respond to attendance</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Participant, confirmed Rehearsal</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Submit a response</v>
+      </c>
+      <c r="F73" t="str">
+        <v>`RehearsalAttendance` status updated</v>
+      </c>
+      <c r="G73" t="str">
+        <v>`RespondRehearsalAttendanceUseCase` Application test</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>ROLE-01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C74" t="str">
+        <v>One Person holds multiple simultaneous roles</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Seed data: `stageart_demo_production_manager` is both an Org A Member and the PrimaryManager of all 3 demo Productions</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Inspect Memberships/Participants for that Person</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Multiple active role rows across different scopes coexist correctly</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Direct DB read of seed data (this session)</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>ROLE-02</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Organization ownership does not imply Production management</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Org Owner not PrimaryManager of a given Production</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Attempt a Production-management action as the Owner</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Denied</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Live curl this session (see ORG-03)</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>ROLE-03</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C76" t="str">
+        <v>PrimaryManager-exclusive gate has no Organization-fallback path</v>
+      </c>
+      <c r="D76" t="str">
+        <v>`ProductionAuthorizationService::canManageProduction()`</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Exactly two paths: PrimaryManager, then ProductionDelegate - no third branch to Organization Membership</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Source review, `docs/09-Authorization/Authorization.md`</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SEED-01</v>
+      </c>
+      <c r="B77" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Seed script creates all 5 roles + edge states</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Clean or previously-cleaned dev DB</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Run `plugin/scripts/seed_web_beta.php`</v>
+      </c>
+      <c r="F77" t="str">
+        <v>7 demo users, 2 Orgs, 3 Productions (published/draft/archived), Memberships in ACTIVE/REQUESTED/REJECTED, Rehearsals with/without confirmation, 1 past-completed</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Ran this session, verified via direct DB reads - see `docs/testing/SeedData.md`</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SEED-02</v>
+      </c>
+      <c r="B78" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Cleanup removes only demo data</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Seed data present, plus unrelated real data</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Run `seed_web_beta_cleanup.php`</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Only `stageart_demo_*` users and `[Sample]`-prefixed Orgs/Productions (and their dependents) removed; other data untouched</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Ran this session - confirmed a real, non-demo Membership row survived cleanup untouched</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SEED-03</v>
+      </c>
+      <c r="B79" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Cleanup is a no-op on a clean DB</v>
+      </c>
+      <c r="D79" t="str">
+        <v>No demo data present</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Run cleanup</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Zero rows affected, no errors</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Ran this session</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
         <v>SEED-04</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B80" t="str">
         <v>SEED DATA</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C80" t="str">
         <v>Re-seed after cleanup is idempotent</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D80" t="str">
         <v>Just cleaned</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E80" t="str">
         <v>Run seed again</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F80" t="str">
         <v>Completes with no unique-constraint conflicts</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G80" t="str">
         <v>Ran this session</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G80"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F80"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -2720,13 +2950,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SEARCH-01</v>
+        <v>PUBLIC-URL-001</v>
       </c>
       <c r="B35" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C35" t="str">
-        <v>Organization search, unauthenticated</v>
+        <v>Organization official URL</v>
       </c>
       <c r="D35" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2740,13 +2970,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SEARCH-02</v>
+        <v>PUBLIC-URL-002</v>
       </c>
       <c r="B36" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C36" t="str">
-        <v>Production search, unauthenticated</v>
+        <v>Production official URL</v>
       </c>
       <c r="D36" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2760,13 +2990,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SEARCH-03</v>
+        <v>PUBLIC-URL-003</v>
       </c>
       <c r="B37" t="str">
-        <v>SEARCH</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C37" t="str">
-        <v>Empty/whitespace query</v>
+        <v>Unauthenticated viewing</v>
       </c>
       <c r="D37" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2780,13 +3010,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>MEM-01</v>
+        <v>PUBLIC-URL-004</v>
       </c>
       <c r="B38" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C38" t="str">
-        <v>Request Organization membership via search</v>
+        <v>PUBLISHED is viewable</v>
       </c>
       <c r="D38" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2800,13 +3030,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MEM-02</v>
+        <v>PUBLIC-URL-005</v>
       </c>
       <c r="B39" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C39" t="str">
-        <v>Admin approves pending request</v>
+        <v>DRAFT is not viewable</v>
       </c>
       <c r="D39" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2820,13 +3050,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MEM-03</v>
+        <v>PUBLIC-URL-006</v>
       </c>
       <c r="B40" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C40" t="str">
-        <v>Admin rejects pending request</v>
+        <v>SCHEDULED before its publish date</v>
       </c>
       <c r="D40" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2840,13 +3070,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MEM-04</v>
+        <v>PUBLIC-URL-007</v>
       </c>
       <c r="B41" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C41" t="str">
-        <v>Re-request after rejection</v>
+        <v>SCHEDULED after its publish date</v>
       </c>
       <c r="D41" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2860,13 +3090,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MEM-05</v>
+        <v>PUBLIC-URL-008</v>
       </c>
       <c r="B42" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C42" t="str">
-        <v>List my memberships (real HTTP)</v>
+        <v>ARCHIVED Production handling</v>
       </c>
       <c r="D42" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2880,13 +3110,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MEM-06</v>
+        <v>PUBLIC-URL-009</v>
       </c>
       <c r="B43" t="str">
-        <v>MEMBERSHIP</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C43" t="str">
-        <v>List pending requests (real HTTP)</v>
+        <v>Search result → Public Page navigation</v>
       </c>
       <c r="D43" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2900,13 +3130,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>JOIN-01</v>
+        <v>PUBLIC-URL-010</v>
       </c>
       <c r="B44" t="str">
-        <v>JOIN KEY</v>
+        <v>PUBLIC</v>
       </c>
       <c r="C44" t="str">
-        <v>Issue Organization Join Key</v>
+        <v>Favorite from the Public Page</v>
       </c>
       <c r="D44" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2920,13 +3150,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>JOIN-02</v>
+        <v>SEARCH-01</v>
       </c>
       <c r="B45" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C45" t="str">
-        <v>Issue Production Join Key</v>
+        <v>Organization search, unauthenticated</v>
       </c>
       <c r="D45" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2940,13 +3170,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>JOIN-03</v>
+        <v>SEARCH-02</v>
       </c>
       <c r="B46" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C46" t="str">
-        <v>Resolve a Join Key</v>
+        <v>Production search, unauthenticated</v>
       </c>
       <c r="D46" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2960,13 +3190,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>JOIN-04</v>
+        <v>SEARCH-03</v>
       </c>
       <c r="B47" t="str">
-        <v>JOIN KEY</v>
+        <v>SEARCH</v>
       </c>
       <c r="C47" t="str">
-        <v>Join via code → request created</v>
+        <v>Empty/whitespace query</v>
       </c>
       <c r="D47" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -2980,13 +3210,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>JOIN-05</v>
+        <v>MEM-01</v>
       </c>
       <c r="B48" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C48" t="str">
-        <v>Disable a Join Key</v>
+        <v>Request Organization membership via search</v>
       </c>
       <c r="D48" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3000,13 +3230,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>JOIN-06</v>
+        <v>MEM-02</v>
       </c>
       <c r="B49" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C49" t="str">
-        <v>Expired/exhausted key rejected</v>
+        <v>Admin approves pending request</v>
       </c>
       <c r="D49" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3020,13 +3250,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>JOIN-07</v>
+        <v>MEM-03</v>
       </c>
       <c r="B50" t="str">
-        <v>JOIN KEY</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C50" t="str">
-        <v>QR is a representation of Join Key, not a separate identity</v>
+        <v>Admin rejects pending request</v>
       </c>
       <c r="D50" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3040,13 +3270,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>FAV-01</v>
+        <v>MEM-04</v>
       </c>
       <c r="B51" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C51" t="str">
-        <v>Favorite an Organization</v>
+        <v>Re-request after rejection</v>
       </c>
       <c r="D51" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3060,13 +3290,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>FAV-02</v>
+        <v>MEM-05</v>
       </c>
       <c r="B52" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C52" t="str">
-        <v>Favorite a Production</v>
+        <v>List my memberships (real HTTP)</v>
       </c>
       <c r="D52" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3080,13 +3310,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>FAV-03</v>
+        <v>MEM-06</v>
       </c>
       <c r="B53" t="str">
-        <v>FAVORITE</v>
+        <v>MEMBERSHIP</v>
       </c>
       <c r="C53" t="str">
-        <v>Remove a Favorite</v>
+        <v>List pending requests (real HTTP)</v>
       </c>
       <c r="D53" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3100,13 +3330,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>FAV-04</v>
+        <v>JOIN-01</v>
       </c>
       <c r="B54" t="str">
-        <v>FAVORITE</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C54" t="str">
-        <v>Cannot favorite an unpublished target</v>
+        <v>Issue Organization Join Key</v>
       </c>
       <c r="D54" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3120,13 +3350,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>REH-01</v>
+        <v>JOIN-02</v>
       </c>
       <c r="B55" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C55" t="str">
-        <v>Create a Rehearsal</v>
+        <v>Issue Production Join Key</v>
       </c>
       <c r="D55" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3140,13 +3370,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>REH-02</v>
+        <v>JOIN-03</v>
       </c>
       <c r="B56" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C56" t="str">
-        <v>Confirm a Rehearsal</v>
+        <v>Resolve a Join Key</v>
       </c>
       <c r="D56" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3160,13 +3390,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>REH-03</v>
+        <v>JOIN-04</v>
       </c>
       <c r="B57" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C57" t="str">
-        <v>Full lifecycle: confirm → activate → complete</v>
+        <v>Join via code → request created</v>
       </c>
       <c r="D57" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3180,13 +3410,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>REH-04</v>
+        <v>JOIN-05</v>
       </c>
       <c r="B58" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C58" t="str">
-        <v>Edit basic info on a non-terminal Rehearsal</v>
+        <v>Disable a Join Key</v>
       </c>
       <c r="D58" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3200,13 +3430,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>REH-05</v>
+        <v>JOIN-06</v>
       </c>
       <c r="B59" t="str">
-        <v>REHEARSAL</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C59" t="str">
-        <v>Cannot edit a COMPLETED/CANCELLED Rehearsal</v>
+        <v>Expired/exhausted key rejected</v>
       </c>
       <c r="D59" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3220,13 +3450,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ATT-01</v>
+        <v>JOIN-07</v>
       </c>
       <c r="B60" t="str">
-        <v>ATTENDANCE</v>
+        <v>JOIN KEY</v>
       </c>
       <c r="C60" t="str">
-        <v>Unconfirmed Rehearsal shows no response control</v>
+        <v>QR is a representation of Join Key, not a separate identity</v>
       </c>
       <c r="D60" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3240,13 +3470,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ATT-02</v>
+        <v>FAV-01</v>
       </c>
       <c r="B61" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C61" t="str">
-        <v>Confirmed Rehearsal shows response control</v>
+        <v>Favorite an Organization</v>
       </c>
       <c r="D61" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3260,13 +3490,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ATT-03</v>
+        <v>FAV-02</v>
       </c>
       <c r="B62" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C62" t="str">
-        <v>Manager views per-member attendance status</v>
+        <v>Favorite a Production</v>
       </c>
       <c r="D62" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3280,13 +3510,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ATT-04</v>
+        <v>FAV-03</v>
       </c>
       <c r="B63" t="str">
-        <v>ATTENDANCE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C63" t="str">
-        <v>Respond to attendance</v>
+        <v>Remove a Favorite</v>
       </c>
       <c r="D63" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3300,13 +3530,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ROLE-01</v>
+        <v>FAV-04</v>
       </c>
       <c r="B64" t="str">
-        <v>ROLE</v>
+        <v>FAVORITE</v>
       </c>
       <c r="C64" t="str">
-        <v>One Person holds multiple simultaneous roles</v>
+        <v>Cannot favorite an unpublished target</v>
       </c>
       <c r="D64" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3320,13 +3550,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ROLE-02</v>
+        <v>REH-01</v>
       </c>
       <c r="B65" t="str">
-        <v>ROLE</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C65" t="str">
-        <v>Organization ownership does not imply Production management</v>
+        <v>Create a Rehearsal</v>
       </c>
       <c r="D65" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3340,13 +3570,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ROLE-03</v>
+        <v>REH-02</v>
       </c>
       <c r="B66" t="str">
-        <v>ROLE</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C66" t="str">
-        <v>PrimaryManager-exclusive gate has no Organization-fallback path</v>
+        <v>Confirm a Rehearsal</v>
       </c>
       <c r="D66" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3360,13 +3590,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SEED-01</v>
+        <v>REH-03</v>
       </c>
       <c r="B67" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C67" t="str">
-        <v>Seed script creates all 5 roles + edge states</v>
+        <v>Full lifecycle: confirm → activate → complete</v>
       </c>
       <c r="D67" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3380,13 +3610,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SEED-02</v>
+        <v>REH-04</v>
       </c>
       <c r="B68" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C68" t="str">
-        <v>Cleanup removes only demo data</v>
+        <v>Edit basic info on a non-terminal Rehearsal</v>
       </c>
       <c r="D68" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3400,13 +3630,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SEED-03</v>
+        <v>REH-05</v>
       </c>
       <c r="B69" t="str">
-        <v>SEED DATA</v>
+        <v>REHEARSAL</v>
       </c>
       <c r="C69" t="str">
-        <v>Cleanup is a no-op on a clean DB</v>
+        <v>Cannot edit a COMPLETED/CANCELLED Rehearsal</v>
       </c>
       <c r="D69" t="str">
         <v>Automated - see TestCases sheet</v>
@@ -3420,27 +3650,227 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
+        <v>ATT-01</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Unconfirmed Rehearsal shows no response control</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E70" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>ATT-02</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Confirmed Rehearsal shows response control</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E71" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>ATT-03</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Manager views per-member attendance status</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E72" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>ATT-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ATTENDANCE</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Respond to attendance</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E73" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>ROLE-01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C74" t="str">
+        <v>One Person holds multiple simultaneous roles</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E74" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>ROLE-02</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Organization ownership does not imply Production management</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E75" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>ROLE-03</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ROLE</v>
+      </c>
+      <c r="C76" t="str">
+        <v>PrimaryManager-exclusive gate has no Organization-fallback path</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E76" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SEED-01</v>
+      </c>
+      <c r="B77" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Seed script creates all 5 roles + edge states</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E77" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SEED-02</v>
+      </c>
+      <c r="B78" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Cleanup removes only demo data</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E78" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SEED-03</v>
+      </c>
+      <c r="B79" t="str">
+        <v>SEED DATA</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Cleanup is a no-op on a clean DB</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E79" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
         <v>SEED-04</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B80" t="str">
         <v>SEED DATA</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C80" t="str">
         <v>Re-seed after cleanup is idempotent</v>
       </c>
-      <c r="D70" t="str">
-        <v>Automated - see TestCases sheet</v>
-      </c>
-      <c r="E70" t="str">
-        <v>NOT RUN</v>
-      </c>
-      <c r="F70" t="str">
+      <c r="D80" t="str">
+        <v>Automated - see TestCases sheet</v>
+      </c>
+      <c r="E80" t="str">
+        <v>NOT RUN</v>
+      </c>
+      <c r="F80" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F80"/>
   </ignoredErrors>
 </worksheet>
 </file>